--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104579_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104579_W14.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>S. DEKKER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4382</v>
+        <v>6.5384</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0983</v>
+        <v>2.5401</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3399</v>
+        <v>3.9984</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6183</v>
+        <v>5.5257</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9394</v>
+        <v>1.4759</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6789</v>
+        <v>4.0498</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6204</v>
+        <v>4.2315</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2397</v>
+        <v>1.2755</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3807</v>
+        <v>2.9559</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9979</v>
+        <v>1.2942</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3003</v>
+        <v>0.2003</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2982</v>
+        <v>1.0939</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>1.805</v>
+        <v>0.4193</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4779</v>
+        <v>-0.5532</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3271</v>
+        <v>0.9726</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. DEKKER</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0312</v>
+        <v>5.4557</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0992</v>
+        <v>2.328</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9319</v>
+        <v>3.1277</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5283</v>
+        <v>3.6253</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4688</v>
+        <v>0.9392</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0595</v>
+        <v>2.6861</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2587</v>
+        <v>2.6048</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2814</v>
+        <v>1.2271</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9772</v>
+        <v>1.3778</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2697</v>
+        <v>1.0204</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1874</v>
+        <v>-0.2879</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0823</v>
+        <v>1.3083</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.8013</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0253</v>
+        <v>-0.2769</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9403</v>
+        <v>1.0782</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6236</v>
+        <v>3.0056</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4337</v>
+        <v>-0.9103</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0574</v>
+        <v>3.916</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9842</v>
+        <v>-0.4865</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2016</v>
+        <v>-1.9837</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1858</v>
+        <v>1.4971</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0154</v>
+        <v>-0.6624</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2242</v>
+        <v>-1.6525</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7912</v>
+        <v>0.9901</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0312</v>
+        <v>0.1759</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4258</v>
+        <v>-0.3312</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3946</v>
+        <v>0.5071</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3595</v>
+        <v>-0.1209</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3266</v>
+        <v>-0.9018</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6861</v>
+        <v>0.7809</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678</v>
+        <v>1.792</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4141</v>
+        <v>1.792</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9801</v>
+        <v>2.0759</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3934</v>
+        <v>-1.546</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3735</v>
+        <v>3.6219</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4711</v>
+        <v>1.9647</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9665</v>
+        <v>-0.2283</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4954</v>
+        <v>2.193</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6163</v>
+        <v>1.976</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6184</v>
+        <v>0.1886</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0021</v>
+        <v>1.7874</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1452</v>
+        <v>-0.0113</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.348</v>
+        <v>-0.4169</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4932</v>
+        <v>0.4057</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1632</v>
+        <v>0.8444</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4426</v>
+        <v>-0.3743</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2794</v>
+        <v>1.2187</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7997</v>
+        <v>0.8603</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>1.405</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1356</v>
+        <v>1.2613</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7694</v>
+        <v>0.7652</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3662</v>
+        <v>0.4961</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1913</v>
+        <v>1.1916</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7648</v>
+        <v>0.764</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4265</v>
+        <v>0.4276</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9085</v>
+        <v>0.9046</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7966</v>
+        <v>0.7929</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0556</v>
+        <v>0.0697</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0835</v>
+        <v>0.2091</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0304</v>
+        <v>0.0461</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0028</v>
+        <v>-0.2501</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0276</v>
+        <v>0.2961</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9346</v>
+        <v>-0.9408</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0304</v>
+        <v>0.0261</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9649</v>
+        <v>-0.9668</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5269</v>
+        <v>-0.5423</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.111</v>
+        <v>-0.1174</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4077</v>
+        <v>-0.3984</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5359</v>
+        <v>0.5527</v>
       </c>
       <c r="T7" t="n">
-        <v>0.369</v>
+        <v>0.1345</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1669</v>
+        <v>0.4182</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.282</v>
+        <v>-0.6635</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6403</v>
+        <v>-1.8291</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3583</v>
+        <v>1.1655</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1593</v>
+        <v>-2.1606</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6636</v>
+        <v>-1.6739</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4957</v>
+        <v>-0.4867</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6135</v>
+        <v>-1.6334</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7255</v>
+        <v>-1.7451</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5458</v>
+        <v>-0.5271</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7431</v>
+        <v>0.3589</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1875</v>
+        <v>-0.3534</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9306</v>
+        <v>0.7123</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0827</v>
+        <v>-0.7714</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9389</v>
+        <v>-1.5933</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8562</v>
+        <v>0.8219</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1071</v>
+        <v>-1.113</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9999</v>
+        <v>-1.999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8929</v>
+        <v>0.886</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.844</v>
+        <v>-0.8729</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0301</v>
+        <v>-2.0414</v>
       </c>
       <c r="L9" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.263</v>
+        <v>-0.2402</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4954</v>
+        <v>-0.1835</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0948</v>
+        <v>-0.7204</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5994</v>
+        <v>0.5369</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3847</v>
+        <v>-1.0349</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1166</v>
+        <v>-0.8333</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2681</v>
+        <v>-0.2016</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4792</v>
+        <v>-0.4714</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2821</v>
+        <v>1.2763</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0218</v>
+        <v>-0.0432</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1411</v>
+        <v>0.1259</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8247</v>
+        <v>0.8481</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5901</v>
+        <v>-0.2543</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0948</v>
+        <v>-0.7901</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5048</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6257</v>
+        <v>-1.2817</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8173</v>
+        <v>-1.5196</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1916</v>
+        <v>0.2379</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5045</v>
+        <v>-1.4984</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5209</v>
+        <v>-0.5199</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9835</v>
+        <v>-0.9785</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.42</v>
+        <v>-0.4249</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0844</v>
+        <v>-1.0734</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2574</v>
+        <v>0.0801</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261</v>
+        <v>-0.3207</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3687</v>
+        <v>0.4008</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6562</v>
+        <v>-1.7178</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9735</v>
+        <v>-3.0951</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3173</v>
+        <v>1.3773</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3262</v>
+        <v>-1.3212</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8008</v>
+        <v>0.8013</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1271</v>
+        <v>-2.1225</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.5508</v>
       </c>
       <c r="K12" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7935</v>
+        <v>-0.7704</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2144</v>
+        <v>0.1498</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5353</v>
+        <v>-0.6322</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7497</v>
+        <v>0.782</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2078</v>
+        <v>12.9137</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.344</v>
+        <v>-5.9435</v>
       </c>
       <c r="F13" t="n">
-        <v>18.5518</v>
+        <v>18.85720000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>5.622199999999998</v>
+        <v>5.591699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.827500000000001</v>
+        <v>-2.869700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>8.449900000000001</v>
+        <v>8.461399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2277</v>
+        <v>4.986999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6354</v>
+        <v>-1.7867</v>
       </c>
       <c r="L13" t="n">
-        <v>6.862899999999999</v>
+        <v>6.7738</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3946999999999997</v>
+        <v>0.6048</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1921</v>
+        <v>-1.083</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5867</v>
+        <v>1.687800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105400000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.939299999999999</v>
+        <v>-7.967200000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0112</v>
+        <v>2.7175</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.6252</v>
+        <v>-4.9279</v>
       </c>
       <c r="U13" t="n">
-        <v>7.636500000000001</v>
+        <v>7.6455</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.499</v>
+        <v>-4.5006</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9928</v>
+        <v>1.9648</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.4918</v>
+        <v>-6.4654</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8136</v>
+        <v>4.9667</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3013</v>
+        <v>3.5117</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5123</v>
+        <v>1.455</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0914</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8838</v>
       </c>
       <c r="I14" t="n">
-        <v>2.223</v>
+        <v>2.2162</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0021</v>
+        <v>2.9835</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0843</v>
+        <v>2.0699</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0893</v>
+        <v>0.1165</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3439</v>
+        <v>-0.2031</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.113</v>
+        <v>-0.8784</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7691</v>
+        <v>0.6752</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7676</v>
+        <v>1.9041</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2721</v>
+        <v>0.8842</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4955</v>
+        <v>1.0198</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1658</v>
+        <v>3.1674</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4284</v>
+        <v>0.4389</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7374</v>
+        <v>2.7286</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7411</v>
+        <v>2.7194</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1292</v>
+        <v>3.1126</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4247</v>
+        <v>0.4481</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8165</v>
+        <v>0.832</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2226</v>
+        <v>-0.0765</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1603</v>
+        <v>-0.193</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3829</v>
+        <v>0.1165</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9963</v>
+        <v>1.0336</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2972</v>
+        <v>-1.3189</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2935</v>
+        <v>2.3525</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1016</v>
+        <v>1.1154</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7285</v>
+        <v>0.7431</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3732</v>
+        <v>0.3724</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1487</v>
+        <v>1.1411</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0471</v>
+        <v>-0.0257</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3814</v>
+        <v>-0.3518</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0434</v>
+        <v>-1.0455</v>
       </c>
       <c r="U16" t="n">
-        <v>0.662</v>
+        <v>0.6937</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8924</v>
+        <v>-0.9589</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5605</v>
+        <v>-1.0965</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3319</v>
+        <v>0.1376</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4787</v>
+        <v>-2.5478</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5715</v>
+        <v>-0.0722</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0502</v>
+        <v>-2.4756</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2157</v>
+        <v>-1.605</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4023</v>
+        <v>-0.1002</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>-1.5048</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.263</v>
+        <v>-0.9428</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9737</v>
+        <v>0.028</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2368</v>
+        <v>-0.9708</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4521</v>
+        <v>0.0441</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1179</v>
+        <v>-0.3534</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.3975</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9522</v>
+        <v>-1.2381</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8439</v>
+        <v>-0.9344</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1083</v>
+        <v>-0.3037</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5584</v>
+        <v>-0.4751</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0795</v>
+        <v>0.5688</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.4789</v>
+        <v>-1.0439</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5918</v>
+        <v>-0.235</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.4212</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4981</v>
+        <v>0.1862</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9666</v>
+        <v>-0.2402</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0142</v>
+        <v>0.99</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9808</v>
+        <v>-1.2301</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0599</v>
+        <v>0.0988</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1179</v>
+        <v>-0.4718</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1778</v>
+        <v>0.5707</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1231</v>
+        <v>-1.4151</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4129</v>
+        <v>-1.7963</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2898</v>
+        <v>0.3812</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.8855</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2382</v>
+        <v>0.2329</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1248</v>
+        <v>-1.1184</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.325</v>
+        <v>-0.3439</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3494</v>
+        <v>0.334</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5617</v>
+        <v>-0.5416</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.444</v>
+        <v>0.1533</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0484</v>
+        <v>-0.4021</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4924</v>
+        <v>0.5554</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7855</v>
+        <v>-1.6233</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4655</v>
+        <v>-2.2704</v>
       </c>
       <c r="F20" t="n">
-        <v>0.68</v>
+        <v>0.647</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2141</v>
+        <v>-2.2284</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4761</v>
+        <v>-0.4822</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.738</v>
+        <v>-1.7462</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.917</v>
+        <v>-0.9553</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1598</v>
+        <v>-0.1798</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2971</v>
+        <v>-1.2731</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4788</v>
+        <v>-0.3055</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3217</v>
+        <v>-1.0875</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8429</v>
+        <v>0.782</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0701</v>
+        <v>-3.0944</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.4518</v>
+        <v>-6.1667</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3817</v>
+        <v>3.0723</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3236</v>
+        <v>1.3098</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0997</v>
+        <v>1.0864</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9198</v>
+        <v>0.8774</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1491</v>
+        <v>1.1162</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4038</v>
+        <v>0.4324</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P21" t="n">
-        <v>-6.3513</v>
+        <v>-6.3737</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2543</v>
+        <v>0.2638</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.113</v>
+        <v>-0.7599</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3673</v>
+        <v>1.0237</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6985</v>
+        <v>-4.3974</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1822</v>
+        <v>-4.8522</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4837</v>
+        <v>0.4549</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9037</v>
+        <v>-4.893</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.876</v>
+        <v>-0.8651</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.0276</v>
+        <v>-4.0279</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.5162</v>
+        <v>-3.5345</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.1454</v>
+        <v>-3.1586</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3875</v>
+        <v>-1.3585</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4092</v>
+        <v>-0.1173</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5999</v>
+        <v>-1.2478</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1907</v>
+        <v>1.1305</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2635</v>
+        <v>-6.6042</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4576</v>
+        <v>-5.3623</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8059</v>
+        <v>-1.2418</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2633</v>
+        <v>-3.2546</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3245</v>
+        <v>0.3354</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.5878</v>
+        <v>-3.5901</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6408</v>
+        <v>-1.6525</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.762</v>
+        <v>-1.7731</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6225</v>
+        <v>-1.6022</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3858</v>
+        <v>-0.7365</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3217</v>
+        <v>-1.2059</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0641</v>
+        <v>0.4694</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.2078</v>
+        <v>-11.427</v>
       </c>
       <c r="E24" t="n">
-        <v>-19.0982</v>
+        <v>-19.4018</v>
       </c>
       <c r="F24" t="n">
-        <v>6.890400000000001</v>
+        <v>7.9748</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.6224</v>
+        <v>-5.5918</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8276</v>
+        <v>2.8698</v>
       </c>
       <c r="I24" t="n">
-        <v>-8.4498</v>
+        <v>-8.461499999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3948</v>
+        <v>-0.6047999999999998</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1921</v>
+        <v>1.083</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5868</v>
+        <v>-1.6877</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.2277</v>
+        <v>-4.9871</v>
       </c>
       <c r="N24" t="n">
-        <v>1.6353</v>
+        <v>1.786799999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.863</v>
+        <v>-6.7738</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.073200000000002</v>
+        <v>-9.1052</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0124</v>
+        <v>-17.0721</v>
       </c>
       <c r="R24" t="n">
-        <v>7.9393</v>
+        <v>7.967300000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0114</v>
+        <v>-1.2307</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.6366</v>
+        <v>-7.645299999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>5.625299999999999</v>
+        <v>6.4146</v>
       </c>
       <c r="V24" t="n">
-        <v>4.4991</v>
+        <v>4.5009</v>
       </c>
       <c r="W24" t="n">
-        <v>5.9455</v>
+        <v>5.920699999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4466</v>
+        <v>-1.4199</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104579_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104579_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.4654</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>1.1609</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104579_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-1.4199</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
